--- a/Data/Input/TransaccionesSAP.xlsx
+++ b/Data/Input/TransaccionesSAP.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aci-cns\Documents\UiPath\AMP22_RequisitosCalidadPedidoProveedor\Data\Input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51398C70-8D4B-4165-833D-709F431162B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F020C5F5-CDFC-4F13-BAEE-DB85F1701884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E7D37262-4DB0-4AD2-A290-68AC6299F871}"/>
   </bookViews>
@@ -20,21 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>Transaction</t>
   </si>
   <si>
     <t>Step1</t>
-  </si>
-  <si>
-    <t>Step2</t>
-  </si>
-  <si>
-    <t>variante</t>
-  </si>
-  <si>
-    <t>ejecutar</t>
   </si>
   <si>
     <t>ZMM026</t>
@@ -44,9 +35,6 @@
   </si>
   <si>
     <t>ZMM051</t>
-  </si>
-  <si>
-    <t>ZPP029_6</t>
   </si>
 </sst>
 </file>
@@ -893,45 +881,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1487AD3F-8DFF-47B2-8A8A-A4855C7319A0}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
       <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
